--- a/databases/PU Level B Book 2.xlsx
+++ b/databases/PU Level B Book 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\전한결\Documents\GitHub\Pattern_worksheet\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\전한결\Documents\worksheet-vercel\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B07D0FF-F8B7-4685-8F6C-32B2C8D49D83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96CC12E-5E22-4FBD-9C65-D77EDA1A861F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pattern Details" sheetId="1" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t>Would you like to …?</t>
   </si>
   <si>
-    <t>I usually [always, often, sometimes, never] ...</t>
-  </si>
-  <si>
     <t>Stop –ing.</t>
   </si>
   <si>
@@ -2590,6 +2587,10 @@
   </si>
   <si>
     <t>종이컵 그만 써.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I usually [always, often, sometimes, never] ….</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2988,7 +2989,7 @@
   <dimension ref="A1:G601"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="59.25" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="32.125" customWidth="1"/>
@@ -3010,7 +3011,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -3033,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3050,10 +3051,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -3073,13 +3074,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3096,7 +3097,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3113,13 +3114,13 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3136,13 +3137,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3159,7 +3160,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3176,13 +3177,13 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3199,13 +3200,13 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -3222,7 +3223,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -3239,13 +3240,13 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -3262,13 +3263,13 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
         <v>40</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -3285,7 +3286,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -3302,13 +3303,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -3325,13 +3326,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
         <v>42</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -3348,7 +3349,7 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -3365,13 +3366,13 @@
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -3388,13 +3389,13 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -3411,7 +3412,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -3428,13 +3429,13 @@
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -3451,13 +3452,13 @@
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -3474,7 +3475,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -3491,13 +3492,13 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -3514,13 +3515,13 @@
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -3537,7 +3538,7 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -3554,13 +3555,13 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -3577,13 +3578,13 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -3600,7 +3601,7 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -3617,13 +3618,13 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -3640,13 +3641,13 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G31" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -3663,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -3680,13 +3681,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -3703,13 +3704,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -3726,7 +3727,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -3743,13 +3744,13 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -3766,13 +3767,13 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" t="s">
         <v>50</v>
-      </c>
-      <c r="G37" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -3789,7 +3790,7 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -3806,13 +3807,13 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -3829,13 +3830,13 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -3852,7 +3853,7 @@
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -3869,13 +3870,13 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G42" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -3892,13 +3893,13 @@
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -3915,7 +3916,7 @@
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -3932,13 +3933,13 @@
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -3955,13 +3956,13 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G46" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -3978,7 +3979,7 @@
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -3995,13 +3996,13 @@
         <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G48" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -4018,13 +4019,13 @@
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -4041,7 +4042,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -4058,13 +4059,13 @@
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G51" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -4081,13 +4082,13 @@
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G52" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -4104,7 +4105,7 @@
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -4121,13 +4122,13 @@
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -4144,13 +4145,13 @@
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G55" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -4167,7 +4168,7 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -4184,13 +4185,13 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G57" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -4207,13 +4208,13 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G58" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -4230,7 +4231,7 @@
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -4247,13 +4248,13 @@
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G60" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -4270,13 +4271,13 @@
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G61" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -4293,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -4310,13 +4311,13 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F63" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G63" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -4333,13 +4334,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F64" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G64" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -4356,7 +4357,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -4373,13 +4374,13 @@
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F66" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G66" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -4396,13 +4397,13 @@
         <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F67" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G67" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -4419,7 +4420,7 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -4436,13 +4437,13 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F69" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G69" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -4459,13 +4460,13 @@
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F70" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G70" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -4482,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -4499,13 +4500,13 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F72" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G72" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -4522,13 +4523,13 @@
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F73" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G73" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -4545,7 +4546,7 @@
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -4562,13 +4563,13 @@
         <v>5</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F75" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G75" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -4585,13 +4586,13 @@
         <v>5</v>
       </c>
       <c r="E76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F76" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G76" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -4608,7 +4609,7 @@
         <v>6</v>
       </c>
       <c r="E77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -4625,13 +4626,13 @@
         <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G78" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -4648,13 +4649,13 @@
         <v>6</v>
       </c>
       <c r="E79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F79" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G79" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -4671,7 +4672,7 @@
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -4688,13 +4689,13 @@
         <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F81" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G81" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -4711,13 +4712,13 @@
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F82" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G82" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -4734,7 +4735,7 @@
         <v>8</v>
       </c>
       <c r="E83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -4751,13 +4752,13 @@
         <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F84" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G84" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -4774,13 +4775,13 @@
         <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F85" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G85" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -4797,7 +4798,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -4814,13 +4815,13 @@
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F87" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G87" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -4837,13 +4838,13 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F88" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G88" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -4860,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="E89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -4877,13 +4878,13 @@
         <v>10</v>
       </c>
       <c r="E90" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F90" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G90" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -4900,13 +4901,13 @@
         <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F91" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G91" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -4923,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -4940,13 +4941,13 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F93" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G93" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -4963,13 +4964,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G94" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -4986,7 +4987,7 @@
         <v>2</v>
       </c>
       <c r="E95" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -5003,13 +5004,13 @@
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F96" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G96" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -5026,13 +5027,13 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F97" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G97" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -5049,7 +5050,7 @@
         <v>3</v>
       </c>
       <c r="E98" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -5066,13 +5067,13 @@
         <v>3</v>
       </c>
       <c r="E99" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F99" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G99" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -5089,13 +5090,13 @@
         <v>3</v>
       </c>
       <c r="E100" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F100" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G100" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -5112,7 +5113,7 @@
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -5129,13 +5130,13 @@
         <v>4</v>
       </c>
       <c r="E102" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F102" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -5152,13 +5153,13 @@
         <v>4</v>
       </c>
       <c r="E103" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G103" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -5175,7 +5176,7 @@
         <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -5192,13 +5193,13 @@
         <v>5</v>
       </c>
       <c r="E105" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F105" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -5215,13 +5216,13 @@
         <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F106" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -5238,7 +5239,7 @@
         <v>6</v>
       </c>
       <c r="E107" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -5255,13 +5256,13 @@
         <v>6</v>
       </c>
       <c r="E108" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F108" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G108" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -5278,13 +5279,13 @@
         <v>6</v>
       </c>
       <c r="E109" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F109" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -5301,7 +5302,7 @@
         <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -5318,13 +5319,13 @@
         <v>7</v>
       </c>
       <c r="E111" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F111" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G111" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -5341,13 +5342,13 @@
         <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F112" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G112" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -5364,7 +5365,7 @@
         <v>8</v>
       </c>
       <c r="E113" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -5381,13 +5382,13 @@
         <v>8</v>
       </c>
       <c r="E114" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F114" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G114" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -5404,13 +5405,13 @@
         <v>8</v>
       </c>
       <c r="E115" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F115" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G115" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -5427,7 +5428,7 @@
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -5444,13 +5445,13 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F117" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G117" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -5467,13 +5468,13 @@
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F118" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G118" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -5490,7 +5491,7 @@
         <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -5507,13 +5508,13 @@
         <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G120" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -5530,13 +5531,13 @@
         <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F121" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G121" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -5553,7 +5554,7 @@
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -5570,13 +5571,13 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
+        <v>76</v>
+      </c>
+      <c r="F123" t="s">
         <v>77</v>
       </c>
-      <c r="F123" t="s">
-        <v>78</v>
-      </c>
       <c r="G123" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -5593,13 +5594,13 @@
         <v>1</v>
       </c>
       <c r="E124" t="s">
+        <v>76</v>
+      </c>
+      <c r="F124" t="s">
         <v>77</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>78</v>
-      </c>
-      <c r="G124" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -5616,7 +5617,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -5633,13 +5634,13 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
+        <v>79</v>
+      </c>
+      <c r="F126" t="s">
         <v>80</v>
       </c>
-      <c r="F126" t="s">
-        <v>81</v>
-      </c>
       <c r="G126" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -5656,13 +5657,13 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
+        <v>79</v>
+      </c>
+      <c r="F127" t="s">
         <v>80</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>81</v>
-      </c>
-      <c r="G127" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -5679,7 +5680,7 @@
         <v>3</v>
       </c>
       <c r="E128" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -5696,13 +5697,13 @@
         <v>3</v>
       </c>
       <c r="E129" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G129" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -5719,13 +5720,13 @@
         <v>3</v>
       </c>
       <c r="E130" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F130" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G130" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -5742,7 +5743,7 @@
         <v>4</v>
       </c>
       <c r="E131" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -5759,13 +5760,13 @@
         <v>4</v>
       </c>
       <c r="E132" t="s">
+        <v>83</v>
+      </c>
+      <c r="F132" t="s">
         <v>84</v>
       </c>
-      <c r="F132" t="s">
-        <v>85</v>
-      </c>
       <c r="G132" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -5782,13 +5783,13 @@
         <v>4</v>
       </c>
       <c r="E133" t="s">
+        <v>83</v>
+      </c>
+      <c r="F133" t="s">
         <v>84</v>
       </c>
-      <c r="F133" t="s">
-        <v>85</v>
-      </c>
       <c r="G133" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -5805,7 +5806,7 @@
         <v>5</v>
       </c>
       <c r="E134" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -5822,13 +5823,13 @@
         <v>5</v>
       </c>
       <c r="E135" t="s">
+        <v>85</v>
+      </c>
+      <c r="F135" t="s">
         <v>86</v>
       </c>
-      <c r="F135" t="s">
-        <v>87</v>
-      </c>
       <c r="G135" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -5845,13 +5846,13 @@
         <v>5</v>
       </c>
       <c r="E136" t="s">
+        <v>85</v>
+      </c>
+      <c r="F136" t="s">
         <v>86</v>
       </c>
-      <c r="F136" t="s">
-        <v>87</v>
-      </c>
       <c r="G136" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -5868,7 +5869,7 @@
         <v>6</v>
       </c>
       <c r="E137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -5885,13 +5886,13 @@
         <v>6</v>
       </c>
       <c r="E138" t="s">
+        <v>87</v>
+      </c>
+      <c r="F138" t="s">
         <v>88</v>
       </c>
-      <c r="F138" t="s">
-        <v>89</v>
-      </c>
       <c r="G138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -5908,13 +5909,13 @@
         <v>6</v>
       </c>
       <c r="E139" t="s">
+        <v>87</v>
+      </c>
+      <c r="F139" t="s">
         <v>88</v>
       </c>
-      <c r="F139" t="s">
-        <v>89</v>
-      </c>
       <c r="G139" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -5931,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -5948,13 +5949,13 @@
         <v>7</v>
       </c>
       <c r="E141" t="s">
+        <v>89</v>
+      </c>
+      <c r="F141" t="s">
         <v>90</v>
       </c>
-      <c r="F141" t="s">
-        <v>91</v>
-      </c>
       <c r="G141" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -5971,13 +5972,13 @@
         <v>7</v>
       </c>
       <c r="E142" t="s">
+        <v>89</v>
+      </c>
+      <c r="F142" t="s">
         <v>90</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>91</v>
-      </c>
-      <c r="G142" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -5994,7 +5995,7 @@
         <v>8</v>
       </c>
       <c r="E143" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -6011,13 +6012,13 @@
         <v>8</v>
       </c>
       <c r="E144" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F144" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G144" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -6034,13 +6035,13 @@
         <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F145" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G145" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -6057,7 +6058,7 @@
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -6074,13 +6075,13 @@
         <v>9</v>
       </c>
       <c r="E147" t="s">
+        <v>93</v>
+      </c>
+      <c r="F147" t="s">
         <v>94</v>
       </c>
-      <c r="F147" t="s">
-        <v>95</v>
-      </c>
       <c r="G147" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -6097,13 +6098,13 @@
         <v>9</v>
       </c>
       <c r="E148" t="s">
+        <v>93</v>
+      </c>
+      <c r="F148" t="s">
         <v>94</v>
       </c>
-      <c r="F148" t="s">
-        <v>95</v>
-      </c>
       <c r="G148" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -6120,7 +6121,7 @@
         <v>10</v>
       </c>
       <c r="E149" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -6137,13 +6138,13 @@
         <v>10</v>
       </c>
       <c r="E150" t="s">
+        <v>95</v>
+      </c>
+      <c r="F150" t="s">
         <v>96</v>
       </c>
-      <c r="F150" t="s">
-        <v>97</v>
-      </c>
       <c r="G150" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -6160,13 +6161,13 @@
         <v>10</v>
       </c>
       <c r="E151" t="s">
+        <v>95</v>
+      </c>
+      <c r="F151" t="s">
         <v>96</v>
       </c>
-      <c r="F151" t="s">
-        <v>97</v>
-      </c>
       <c r="G151" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -6183,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -6200,13 +6201,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="s">
+        <v>97</v>
+      </c>
+      <c r="F153" t="s">
         <v>98</v>
       </c>
-      <c r="F153" t="s">
-        <v>99</v>
-      </c>
       <c r="G153" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -6223,13 +6224,13 @@
         <v>1</v>
       </c>
       <c r="E154" t="s">
+        <v>97</v>
+      </c>
+      <c r="F154" t="s">
         <v>98</v>
       </c>
-      <c r="F154" t="s">
-        <v>99</v>
-      </c>
       <c r="G154" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
@@ -6246,7 +6247,7 @@
         <v>2</v>
       </c>
       <c r="E155" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -6263,13 +6264,13 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
+        <v>99</v>
+      </c>
+      <c r="F156" t="s">
         <v>100</v>
       </c>
-      <c r="F156" t="s">
-        <v>101</v>
-      </c>
       <c r="G156" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -6286,13 +6287,13 @@
         <v>2</v>
       </c>
       <c r="E157" t="s">
+        <v>99</v>
+      </c>
+      <c r="F157" t="s">
         <v>100</v>
       </c>
-      <c r="F157" t="s">
-        <v>101</v>
-      </c>
       <c r="G157" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -6309,7 +6310,7 @@
         <v>3</v>
       </c>
       <c r="E158" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -6326,13 +6327,13 @@
         <v>3</v>
       </c>
       <c r="E159" t="s">
+        <v>101</v>
+      </c>
+      <c r="F159" t="s">
         <v>102</v>
       </c>
-      <c r="F159" t="s">
-        <v>103</v>
-      </c>
       <c r="G159" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -6349,13 +6350,13 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
+        <v>101</v>
+      </c>
+      <c r="F160" t="s">
         <v>102</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>103</v>
-      </c>
-      <c r="G160" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -6372,7 +6373,7 @@
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -6389,13 +6390,13 @@
         <v>4</v>
       </c>
       <c r="E162" t="s">
+        <v>104</v>
+      </c>
+      <c r="F162" t="s">
         <v>105</v>
       </c>
-      <c r="F162" t="s">
-        <v>106</v>
-      </c>
       <c r="G162" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
@@ -6412,13 +6413,13 @@
         <v>4</v>
       </c>
       <c r="E163" t="s">
+        <v>104</v>
+      </c>
+      <c r="F163" t="s">
         <v>105</v>
       </c>
-      <c r="F163" t="s">
-        <v>106</v>
-      </c>
       <c r="G163" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
@@ -6435,7 +6436,7 @@
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -6452,13 +6453,13 @@
         <v>5</v>
       </c>
       <c r="E165" t="s">
+        <v>106</v>
+      </c>
+      <c r="F165" t="s">
         <v>107</v>
       </c>
-      <c r="F165" t="s">
-        <v>108</v>
-      </c>
       <c r="G165" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
@@ -6475,13 +6476,13 @@
         <v>5</v>
       </c>
       <c r="E166" t="s">
+        <v>106</v>
+      </c>
+      <c r="F166" t="s">
         <v>107</v>
       </c>
-      <c r="F166" t="s">
-        <v>108</v>
-      </c>
       <c r="G166" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
@@ -6498,7 +6499,7 @@
         <v>6</v>
       </c>
       <c r="E167" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
@@ -6515,13 +6516,13 @@
         <v>6</v>
       </c>
       <c r="E168" t="s">
+        <v>108</v>
+      </c>
+      <c r="F168" t="s">
         <v>109</v>
       </c>
-      <c r="F168" t="s">
-        <v>110</v>
-      </c>
       <c r="G168" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
@@ -6538,13 +6539,13 @@
         <v>6</v>
       </c>
       <c r="E169" t="s">
+        <v>108</v>
+      </c>
+      <c r="F169" t="s">
         <v>109</v>
       </c>
-      <c r="F169" t="s">
-        <v>110</v>
-      </c>
       <c r="G169" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
@@ -6561,7 +6562,7 @@
         <v>7</v>
       </c>
       <c r="E170" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -6578,13 +6579,13 @@
         <v>7</v>
       </c>
       <c r="E171" t="s">
+        <v>110</v>
+      </c>
+      <c r="F171" t="s">
         <v>111</v>
       </c>
-      <c r="F171" t="s">
-        <v>112</v>
-      </c>
       <c r="G171" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
@@ -6601,13 +6602,13 @@
         <v>7</v>
       </c>
       <c r="E172" t="s">
+        <v>110</v>
+      </c>
+      <c r="F172" t="s">
         <v>111</v>
       </c>
-      <c r="F172" t="s">
-        <v>112</v>
-      </c>
       <c r="G172" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
@@ -6624,7 +6625,7 @@
         <v>8</v>
       </c>
       <c r="E173" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
@@ -6641,13 +6642,13 @@
         <v>8</v>
       </c>
       <c r="E174" t="s">
+        <v>112</v>
+      </c>
+      <c r="F174" t="s">
         <v>113</v>
       </c>
-      <c r="F174" t="s">
-        <v>114</v>
-      </c>
       <c r="G174" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
@@ -6664,13 +6665,13 @@
         <v>8</v>
       </c>
       <c r="E175" t="s">
+        <v>112</v>
+      </c>
+      <c r="F175" t="s">
         <v>113</v>
       </c>
-      <c r="F175" t="s">
-        <v>114</v>
-      </c>
       <c r="G175" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
@@ -6687,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
@@ -6704,13 +6705,13 @@
         <v>9</v>
       </c>
       <c r="E177" t="s">
+        <v>114</v>
+      </c>
+      <c r="F177" t="s">
         <v>115</v>
       </c>
-      <c r="F177" t="s">
-        <v>116</v>
-      </c>
       <c r="G177" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
@@ -6727,13 +6728,13 @@
         <v>9</v>
       </c>
       <c r="E178" t="s">
+        <v>114</v>
+      </c>
+      <c r="F178" t="s">
         <v>115</v>
       </c>
-      <c r="F178" t="s">
-        <v>116</v>
-      </c>
       <c r="G178" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
@@ -6750,7 +6751,7 @@
         <v>10</v>
       </c>
       <c r="E179" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
@@ -6767,13 +6768,13 @@
         <v>10</v>
       </c>
       <c r="E180" t="s">
+        <v>116</v>
+      </c>
+      <c r="F180" t="s">
         <v>117</v>
       </c>
-      <c r="F180" t="s">
-        <v>118</v>
-      </c>
       <c r="G180" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
@@ -6790,13 +6791,13 @@
         <v>10</v>
       </c>
       <c r="E181" t="s">
+        <v>116</v>
+      </c>
+      <c r="F181" t="s">
         <v>117</v>
       </c>
-      <c r="F181" t="s">
-        <v>118</v>
-      </c>
       <c r="G181" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6813,7 +6814,7 @@
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
@@ -6832,13 +6833,13 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F183" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G183" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6855,13 +6856,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F184" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G184" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -6878,7 +6879,7 @@
         <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
@@ -6895,13 +6896,13 @@
         <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G186" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
@@ -6918,13 +6919,13 @@
         <v>2</v>
       </c>
       <c r="E187" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F187" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G187" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
@@ -6941,7 +6942,7 @@
         <v>3</v>
       </c>
       <c r="E188" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
@@ -6958,13 +6959,13 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F189" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
@@ -6981,13 +6982,13 @@
         <v>3</v>
       </c>
       <c r="E190" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F190" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G190" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -7004,7 +7005,7 @@
         <v>4</v>
       </c>
       <c r="E191" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
@@ -7021,13 +7022,13 @@
         <v>4</v>
       </c>
       <c r="E192" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F192" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G192" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -7044,13 +7045,13 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F193" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G193" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -7067,7 +7068,7 @@
         <v>5</v>
       </c>
       <c r="E194" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -7084,13 +7085,13 @@
         <v>5</v>
       </c>
       <c r="E195" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F195" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G195" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -7107,13 +7108,13 @@
         <v>5</v>
       </c>
       <c r="E196" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F196" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G196" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -7130,7 +7131,7 @@
         <v>6</v>
       </c>
       <c r="E197" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -7147,13 +7148,13 @@
         <v>6</v>
       </c>
       <c r="E198" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F198" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G198" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -7170,13 +7171,13 @@
         <v>6</v>
       </c>
       <c r="E199" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F199" t="s">
+        <v>123</v>
+      </c>
+      <c r="G199" t="s">
         <v>124</v>
-      </c>
-      <c r="G199" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -7193,7 +7194,7 @@
         <v>7</v>
       </c>
       <c r="E200" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
@@ -7210,13 +7211,13 @@
         <v>7</v>
       </c>
       <c r="E201" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F201" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G201" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
@@ -7233,13 +7234,13 @@
         <v>7</v>
       </c>
       <c r="E202" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F202" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G202" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -7256,7 +7257,7 @@
         <v>8</v>
       </c>
       <c r="E203" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
@@ -7273,13 +7274,13 @@
         <v>8</v>
       </c>
       <c r="E204" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F204" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G204" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
@@ -7296,13 +7297,13 @@
         <v>8</v>
       </c>
       <c r="E205" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F205" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G205" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
@@ -7319,7 +7320,7 @@
         <v>9</v>
       </c>
       <c r="E206" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
@@ -7336,13 +7337,13 @@
         <v>9</v>
       </c>
       <c r="E207" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F207" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G207" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
@@ -7359,13 +7360,13 @@
         <v>9</v>
       </c>
       <c r="E208" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F208" t="s">
+        <v>127</v>
+      </c>
+      <c r="G208" t="s">
         <v>128</v>
-      </c>
-      <c r="G208" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
@@ -7382,7 +7383,7 @@
         <v>10</v>
       </c>
       <c r="E209" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -7399,13 +7400,13 @@
         <v>10</v>
       </c>
       <c r="E210" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F210" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G210" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
@@ -7422,13 +7423,13 @@
         <v>10</v>
       </c>
       <c r="E211" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F211" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G211" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
@@ -7445,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
@@ -7462,10 +7463,10 @@
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F213" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G213" t="s">
         <v>11</v>
@@ -7485,13 +7486,13 @@
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F214" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G214" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
@@ -7508,7 +7509,7 @@
         <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -7525,13 +7526,13 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F216" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G216" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -7548,13 +7549,13 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F217" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G217" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -7571,7 +7572,7 @@
         <v>3</v>
       </c>
       <c r="E218" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -7588,13 +7589,13 @@
         <v>3</v>
       </c>
       <c r="E219" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F219" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G219" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -7611,13 +7612,13 @@
         <v>3</v>
       </c>
       <c r="E220" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F220" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G220" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -7634,7 +7635,7 @@
         <v>4</v>
       </c>
       <c r="E221" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -7651,13 +7652,13 @@
         <v>4</v>
       </c>
       <c r="E222" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F222" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G222" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -7674,13 +7675,13 @@
         <v>4</v>
       </c>
       <c r="E223" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F223" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G223" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -7697,7 +7698,7 @@
         <v>5</v>
       </c>
       <c r="E224" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -7714,13 +7715,13 @@
         <v>5</v>
       </c>
       <c r="E225" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F225" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G225" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -7737,13 +7738,13 @@
         <v>5</v>
       </c>
       <c r="E226" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F226" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G226" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -7760,7 +7761,7 @@
         <v>6</v>
       </c>
       <c r="E227" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -7777,13 +7778,13 @@
         <v>6</v>
       </c>
       <c r="E228" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F228" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G228" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -7800,13 +7801,13 @@
         <v>6</v>
       </c>
       <c r="E229" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F229" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G229" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -7823,7 +7824,7 @@
         <v>7</v>
       </c>
       <c r="E230" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -7840,13 +7841,13 @@
         <v>7</v>
       </c>
       <c r="E231" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F231" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G231" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -7863,13 +7864,13 @@
         <v>7</v>
       </c>
       <c r="E232" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F232" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G232" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -7886,7 +7887,7 @@
         <v>8</v>
       </c>
       <c r="E233" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -7903,13 +7904,13 @@
         <v>8</v>
       </c>
       <c r="E234" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F234" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G234" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -7926,13 +7927,13 @@
         <v>8</v>
       </c>
       <c r="E235" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F235" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G235" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -7949,7 +7950,7 @@
         <v>9</v>
       </c>
       <c r="E236" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -7966,13 +7967,13 @@
         <v>9</v>
       </c>
       <c r="E237" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F237" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G237" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -7989,13 +7990,13 @@
         <v>9</v>
       </c>
       <c r="E238" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F238" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G238" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -8012,7 +8013,7 @@
         <v>10</v>
       </c>
       <c r="E239" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -8029,13 +8030,13 @@
         <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F240" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G240" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -8052,13 +8053,13 @@
         <v>10</v>
       </c>
       <c r="E241" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F241" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G241" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -8075,7 +8076,7 @@
         <v>1</v>
       </c>
       <c r="E242" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -8092,13 +8093,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="s">
+        <v>140</v>
+      </c>
+      <c r="F243" t="s">
         <v>141</v>
       </c>
-      <c r="F243" t="s">
-        <v>142</v>
-      </c>
       <c r="G243" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -8115,13 +8116,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="s">
+        <v>140</v>
+      </c>
+      <c r="F244" t="s">
         <v>141</v>
       </c>
-      <c r="F244" t="s">
-        <v>142</v>
-      </c>
       <c r="G244" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -8138,7 +8139,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -8155,13 +8156,13 @@
         <v>2</v>
       </c>
       <c r="E246" t="s">
+        <v>142</v>
+      </c>
+      <c r="F246" t="s">
         <v>143</v>
       </c>
-      <c r="F246" t="s">
-        <v>144</v>
-      </c>
       <c r="G246" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -8178,13 +8179,13 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
+        <v>142</v>
+      </c>
+      <c r="F247" t="s">
         <v>143</v>
       </c>
-      <c r="F247" t="s">
-        <v>144</v>
-      </c>
       <c r="G247" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -8201,7 +8202,7 @@
         <v>3</v>
       </c>
       <c r="E248" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -8218,13 +8219,13 @@
         <v>3</v>
       </c>
       <c r="E249" t="s">
+        <v>144</v>
+      </c>
+      <c r="F249" t="s">
         <v>145</v>
       </c>
-      <c r="F249" t="s">
-        <v>146</v>
-      </c>
       <c r="G249" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -8241,13 +8242,13 @@
         <v>3</v>
       </c>
       <c r="E250" t="s">
+        <v>144</v>
+      </c>
+      <c r="F250" t="s">
         <v>145</v>
       </c>
-      <c r="F250" t="s">
-        <v>146</v>
-      </c>
       <c r="G250" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -8264,7 +8265,7 @@
         <v>4</v>
       </c>
       <c r="E251" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -8281,13 +8282,13 @@
         <v>4</v>
       </c>
       <c r="E252" t="s">
+        <v>146</v>
+      </c>
+      <c r="F252" t="s">
         <v>147</v>
       </c>
-      <c r="F252" t="s">
-        <v>148</v>
-      </c>
       <c r="G252" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -8304,13 +8305,13 @@
         <v>4</v>
       </c>
       <c r="E253" t="s">
+        <v>146</v>
+      </c>
+      <c r="F253" t="s">
         <v>147</v>
       </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
         <v>148</v>
-      </c>
-      <c r="G253" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -8327,7 +8328,7 @@
         <v>5</v>
       </c>
       <c r="E254" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -8344,13 +8345,13 @@
         <v>5</v>
       </c>
       <c r="E255" t="s">
+        <v>149</v>
+      </c>
+      <c r="F255" t="s">
         <v>150</v>
       </c>
-      <c r="F255" t="s">
-        <v>151</v>
-      </c>
       <c r="G255" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -8367,13 +8368,13 @@
         <v>5</v>
       </c>
       <c r="E256" t="s">
+        <v>149</v>
+      </c>
+      <c r="F256" t="s">
         <v>150</v>
       </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
         <v>151</v>
-      </c>
-      <c r="G256" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -8390,7 +8391,7 @@
         <v>6</v>
       </c>
       <c r="E257" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -8407,13 +8408,13 @@
         <v>6</v>
       </c>
       <c r="E258" t="s">
+        <v>152</v>
+      </c>
+      <c r="F258" t="s">
         <v>153</v>
       </c>
-      <c r="F258" t="s">
-        <v>154</v>
-      </c>
       <c r="G258" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -8430,13 +8431,13 @@
         <v>6</v>
       </c>
       <c r="E259" t="s">
+        <v>152</v>
+      </c>
+      <c r="F259" t="s">
         <v>153</v>
       </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
         <v>154</v>
-      </c>
-      <c r="G259" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -8453,7 +8454,7 @@
         <v>7</v>
       </c>
       <c r="E260" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -8470,13 +8471,13 @@
         <v>7</v>
       </c>
       <c r="E261" t="s">
+        <v>155</v>
+      </c>
+      <c r="F261" t="s">
         <v>156</v>
       </c>
-      <c r="F261" t="s">
-        <v>157</v>
-      </c>
       <c r="G261" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -8493,13 +8494,13 @@
         <v>7</v>
       </c>
       <c r="E262" t="s">
+        <v>155</v>
+      </c>
+      <c r="F262" t="s">
         <v>156</v>
       </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
         <v>157</v>
-      </c>
-      <c r="G262" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -8516,7 +8517,7 @@
         <v>8</v>
       </c>
       <c r="E263" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -8533,13 +8534,13 @@
         <v>8</v>
       </c>
       <c r="E264" t="s">
+        <v>158</v>
+      </c>
+      <c r="F264" t="s">
         <v>159</v>
       </c>
-      <c r="F264" t="s">
-        <v>160</v>
-      </c>
       <c r="G264" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -8556,13 +8557,13 @@
         <v>8</v>
       </c>
       <c r="E265" t="s">
+        <v>158</v>
+      </c>
+      <c r="F265" t="s">
         <v>159</v>
       </c>
-      <c r="F265" t="s">
+      <c r="G265" t="s">
         <v>160</v>
-      </c>
-      <c r="G265" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -8579,7 +8580,7 @@
         <v>9</v>
       </c>
       <c r="E266" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -8596,13 +8597,13 @@
         <v>9</v>
       </c>
       <c r="E267" t="s">
+        <v>161</v>
+      </c>
+      <c r="F267" t="s">
         <v>162</v>
       </c>
-      <c r="F267" t="s">
-        <v>163</v>
-      </c>
       <c r="G267" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -8619,13 +8620,13 @@
         <v>9</v>
       </c>
       <c r="E268" t="s">
+        <v>161</v>
+      </c>
+      <c r="F268" t="s">
         <v>162</v>
       </c>
-      <c r="F268" t="s">
+      <c r="G268" t="s">
         <v>163</v>
-      </c>
-      <c r="G268" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -8642,7 +8643,7 @@
         <v>10</v>
       </c>
       <c r="E269" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -8659,13 +8660,13 @@
         <v>10</v>
       </c>
       <c r="E270" t="s">
+        <v>164</v>
+      </c>
+      <c r="F270" t="s">
         <v>165</v>
       </c>
-      <c r="F270" t="s">
-        <v>166</v>
-      </c>
       <c r="G270" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -8682,13 +8683,13 @@
         <v>10</v>
       </c>
       <c r="E271" t="s">
+        <v>164</v>
+      </c>
+      <c r="F271" t="s">
         <v>165</v>
       </c>
-      <c r="F271" t="s">
+      <c r="G271" t="s">
         <v>166</v>
-      </c>
-      <c r="G271" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -8705,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="E272" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -8722,13 +8723,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="s">
+        <v>167</v>
+      </c>
+      <c r="F273" t="s">
         <v>168</v>
       </c>
-      <c r="F273" t="s">
-        <v>169</v>
-      </c>
       <c r="G273" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -8745,13 +8746,13 @@
         <v>1</v>
       </c>
       <c r="E274" t="s">
+        <v>167</v>
+      </c>
+      <c r="F274" t="s">
         <v>168</v>
       </c>
-      <c r="F274" t="s">
-        <v>169</v>
-      </c>
       <c r="G274" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -8768,7 +8769,7 @@
         <v>2</v>
       </c>
       <c r="E275" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -8785,10 +8786,10 @@
         <v>2</v>
       </c>
       <c r="E276" t="s">
+        <v>169</v>
+      </c>
+      <c r="F276" t="s">
         <v>170</v>
-      </c>
-      <c r="F276" t="s">
-        <v>171</v>
       </c>
       <c r="G276" t="s">
         <v>9</v>
@@ -8808,13 +8809,13 @@
         <v>2</v>
       </c>
       <c r="E277" t="s">
+        <v>169</v>
+      </c>
+      <c r="F277" t="s">
         <v>170</v>
       </c>
-      <c r="F277" t="s">
-        <v>171</v>
-      </c>
       <c r="G277" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -8831,7 +8832,7 @@
         <v>3</v>
       </c>
       <c r="E278" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -8848,13 +8849,13 @@
         <v>3</v>
       </c>
       <c r="E279" t="s">
+        <v>171</v>
+      </c>
+      <c r="F279" t="s">
         <v>172</v>
       </c>
-      <c r="F279" t="s">
-        <v>173</v>
-      </c>
       <c r="G279" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -8871,13 +8872,13 @@
         <v>3</v>
       </c>
       <c r="E280" t="s">
+        <v>171</v>
+      </c>
+      <c r="F280" t="s">
         <v>172</v>
       </c>
-      <c r="F280" t="s">
-        <v>173</v>
-      </c>
       <c r="G280" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -8894,7 +8895,7 @@
         <v>4</v>
       </c>
       <c r="E281" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -8911,13 +8912,13 @@
         <v>4</v>
       </c>
       <c r="E282" t="s">
+        <v>173</v>
+      </c>
+      <c r="F282" t="s">
         <v>174</v>
       </c>
-      <c r="F282" t="s">
-        <v>175</v>
-      </c>
       <c r="G282" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -8934,13 +8935,13 @@
         <v>4</v>
       </c>
       <c r="E283" t="s">
+        <v>173</v>
+      </c>
+      <c r="F283" t="s">
         <v>174</v>
       </c>
-      <c r="F283" t="s">
-        <v>175</v>
-      </c>
       <c r="G283" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -8957,7 +8958,7 @@
         <v>5</v>
       </c>
       <c r="E284" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -8974,13 +8975,13 @@
         <v>5</v>
       </c>
       <c r="E285" t="s">
+        <v>175</v>
+      </c>
+      <c r="F285" t="s">
         <v>176</v>
       </c>
-      <c r="F285" t="s">
-        <v>177</v>
-      </c>
       <c r="G285" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -8997,13 +8998,13 @@
         <v>5</v>
       </c>
       <c r="E286" t="s">
+        <v>175</v>
+      </c>
+      <c r="F286" t="s">
         <v>176</v>
       </c>
-      <c r="F286" t="s">
-        <v>177</v>
-      </c>
       <c r="G286" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -9020,7 +9021,7 @@
         <v>6</v>
       </c>
       <c r="E287" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -9037,13 +9038,13 @@
         <v>6</v>
       </c>
       <c r="E288" t="s">
+        <v>177</v>
+      </c>
+      <c r="F288" t="s">
         <v>178</v>
       </c>
-      <c r="F288" t="s">
-        <v>179</v>
-      </c>
       <c r="G288" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -9060,13 +9061,13 @@
         <v>6</v>
       </c>
       <c r="E289" t="s">
+        <v>177</v>
+      </c>
+      <c r="F289" t="s">
         <v>178</v>
       </c>
-      <c r="F289" t="s">
-        <v>179</v>
-      </c>
       <c r="G289" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -9083,7 +9084,7 @@
         <v>7</v>
       </c>
       <c r="E290" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -9100,13 +9101,13 @@
         <v>7</v>
       </c>
       <c r="E291" t="s">
+        <v>179</v>
+      </c>
+      <c r="F291" t="s">
         <v>180</v>
       </c>
-      <c r="F291" t="s">
-        <v>181</v>
-      </c>
       <c r="G291" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -9123,13 +9124,13 @@
         <v>7</v>
       </c>
       <c r="E292" t="s">
+        <v>179</v>
+      </c>
+      <c r="F292" t="s">
         <v>180</v>
       </c>
-      <c r="F292" t="s">
-        <v>181</v>
-      </c>
       <c r="G292" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -9146,7 +9147,7 @@
         <v>8</v>
       </c>
       <c r="E293" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -9163,13 +9164,13 @@
         <v>8</v>
       </c>
       <c r="E294" t="s">
+        <v>181</v>
+      </c>
+      <c r="F294" t="s">
         <v>182</v>
       </c>
-      <c r="F294" t="s">
-        <v>183</v>
-      </c>
       <c r="G294" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -9186,13 +9187,13 @@
         <v>8</v>
       </c>
       <c r="E295" t="s">
+        <v>181</v>
+      </c>
+      <c r="F295" t="s">
         <v>182</v>
       </c>
-      <c r="F295" t="s">
-        <v>183</v>
-      </c>
       <c r="G295" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -9209,7 +9210,7 @@
         <v>9</v>
       </c>
       <c r="E296" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -9226,13 +9227,13 @@
         <v>9</v>
       </c>
       <c r="E297" t="s">
+        <v>183</v>
+      </c>
+      <c r="F297" t="s">
         <v>184</v>
       </c>
-      <c r="F297" t="s">
-        <v>185</v>
-      </c>
       <c r="G297" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -9249,13 +9250,13 @@
         <v>9</v>
       </c>
       <c r="E298" t="s">
+        <v>183</v>
+      </c>
+      <c r="F298" t="s">
         <v>184</v>
       </c>
-      <c r="F298" t="s">
+      <c r="G298" t="s">
         <v>185</v>
-      </c>
-      <c r="G298" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -9272,7 +9273,7 @@
         <v>10</v>
       </c>
       <c r="E299" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -9289,13 +9290,13 @@
         <v>10</v>
       </c>
       <c r="E300" t="s">
+        <v>186</v>
+      </c>
+      <c r="F300" t="s">
         <v>187</v>
       </c>
-      <c r="F300" t="s">
-        <v>188</v>
-      </c>
       <c r="G300" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -9312,13 +9313,13 @@
         <v>10</v>
       </c>
       <c r="E301" t="s">
+        <v>186</v>
+      </c>
+      <c r="F301" t="s">
         <v>187</v>
       </c>
-      <c r="F301" t="s">
-        <v>188</v>
-      </c>
       <c r="G301" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="302" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -9335,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F302"/>
       <c r="G302"/>
@@ -9354,13 +9355,13 @@
         <v>1</v>
       </c>
       <c r="E303" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F303" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G303" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -9377,13 +9378,13 @@
         <v>1</v>
       </c>
       <c r="E304" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F304" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G304" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -9400,7 +9401,7 @@
         <v>2</v>
       </c>
       <c r="E305" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -9417,13 +9418,13 @@
         <v>2</v>
       </c>
       <c r="E306" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F306" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G306" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -9440,13 +9441,13 @@
         <v>2</v>
       </c>
       <c r="E307" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F307" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G307" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -9463,7 +9464,7 @@
         <v>3</v>
       </c>
       <c r="E308" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -9480,13 +9481,13 @@
         <v>3</v>
       </c>
       <c r="E309" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F309" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G309" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -9503,13 +9504,13 @@
         <v>3</v>
       </c>
       <c r="E310" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F310" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G310" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -9526,7 +9527,7 @@
         <v>4</v>
       </c>
       <c r="E311" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -9543,13 +9544,13 @@
         <v>4</v>
       </c>
       <c r="E312" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F312" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G312" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -9566,13 +9567,13 @@
         <v>4</v>
       </c>
       <c r="E313" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F313" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G313" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -9589,7 +9590,7 @@
         <v>5</v>
       </c>
       <c r="E314" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -9606,13 +9607,13 @@
         <v>5</v>
       </c>
       <c r="E315" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F315" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G315" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -9629,13 +9630,13 @@
         <v>5</v>
       </c>
       <c r="E316" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F316" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G316" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -9652,7 +9653,7 @@
         <v>6</v>
       </c>
       <c r="E317" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -9669,13 +9670,13 @@
         <v>6</v>
       </c>
       <c r="E318" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F318" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G318" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -9692,13 +9693,13 @@
         <v>6</v>
       </c>
       <c r="E319" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F319" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G319" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -9715,7 +9716,7 @@
         <v>7</v>
       </c>
       <c r="E320" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -9732,13 +9733,13 @@
         <v>7</v>
       </c>
       <c r="E321" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F321" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G321" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -9755,13 +9756,13 @@
         <v>7</v>
       </c>
       <c r="E322" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F322" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G322" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -9778,7 +9779,7 @@
         <v>8</v>
       </c>
       <c r="E323" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -9795,13 +9796,13 @@
         <v>8</v>
       </c>
       <c r="E324" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F324" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G324" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -9818,13 +9819,13 @@
         <v>8</v>
       </c>
       <c r="E325" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F325" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G325" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -9841,7 +9842,7 @@
         <v>9</v>
       </c>
       <c r="E326" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -9858,13 +9859,13 @@
         <v>9</v>
       </c>
       <c r="E327" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F327" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G327" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -9881,13 +9882,13 @@
         <v>9</v>
       </c>
       <c r="E328" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F328" t="s">
+        <v>196</v>
+      </c>
+      <c r="G328" t="s">
         <v>197</v>
-      </c>
-      <c r="G328" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -9904,7 +9905,7 @@
         <v>10</v>
       </c>
       <c r="E329" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -9921,13 +9922,13 @@
         <v>10</v>
       </c>
       <c r="E330" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F330" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G330" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -9944,13 +9945,13 @@
         <v>10</v>
       </c>
       <c r="E331" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F331" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G331" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -9967,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="E332" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -9984,13 +9985,13 @@
         <v>1</v>
       </c>
       <c r="E333" t="s">
+        <v>199</v>
+      </c>
+      <c r="F333" t="s">
         <v>200</v>
       </c>
-      <c r="F333" t="s">
-        <v>201</v>
-      </c>
       <c r="G333" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -10007,13 +10008,13 @@
         <v>1</v>
       </c>
       <c r="E334" t="s">
+        <v>199</v>
+      </c>
+      <c r="F334" t="s">
         <v>200</v>
       </c>
-      <c r="F334" t="s">
-        <v>201</v>
-      </c>
       <c r="G334" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -10030,7 +10031,7 @@
         <v>2</v>
       </c>
       <c r="E335" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
@@ -10047,13 +10048,13 @@
         <v>2</v>
       </c>
       <c r="E336" t="s">
+        <v>201</v>
+      </c>
+      <c r="F336" t="s">
         <v>202</v>
       </c>
-      <c r="F336" t="s">
-        <v>203</v>
-      </c>
       <c r="G336" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
@@ -10070,13 +10071,13 @@
         <v>2</v>
       </c>
       <c r="E337" t="s">
+        <v>201</v>
+      </c>
+      <c r="F337" t="s">
         <v>202</v>
       </c>
-      <c r="F337" t="s">
-        <v>203</v>
-      </c>
       <c r="G337" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
@@ -10093,7 +10094,7 @@
         <v>3</v>
       </c>
       <c r="E338" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
@@ -10110,13 +10111,13 @@
         <v>3</v>
       </c>
       <c r="E339" t="s">
+        <v>203</v>
+      </c>
+      <c r="F339" t="s">
         <v>204</v>
       </c>
-      <c r="F339" t="s">
-        <v>205</v>
-      </c>
       <c r="G339" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
@@ -10133,13 +10134,13 @@
         <v>3</v>
       </c>
       <c r="E340" t="s">
+        <v>203</v>
+      </c>
+      <c r="F340" t="s">
         <v>204</v>
       </c>
-      <c r="F340" t="s">
-        <v>205</v>
-      </c>
       <c r="G340" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
@@ -10156,7 +10157,7 @@
         <v>4</v>
       </c>
       <c r="E341" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
@@ -10173,13 +10174,13 @@
         <v>4</v>
       </c>
       <c r="E342" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F342" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G342" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
@@ -10196,13 +10197,13 @@
         <v>4</v>
       </c>
       <c r="E343" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F343" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G343" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
@@ -10219,7 +10220,7 @@
         <v>5</v>
       </c>
       <c r="E344" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
@@ -10236,13 +10237,13 @@
         <v>5</v>
       </c>
       <c r="E345" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F345" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G345" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
@@ -10259,13 +10260,13 @@
         <v>5</v>
       </c>
       <c r="E346" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F346" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G346" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
@@ -10282,7 +10283,7 @@
         <v>6</v>
       </c>
       <c r="E347" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
@@ -10299,13 +10300,13 @@
         <v>6</v>
       </c>
       <c r="E348" t="s">
+        <v>207</v>
+      </c>
+      <c r="F348" t="s">
         <v>208</v>
       </c>
-      <c r="F348" t="s">
-        <v>209</v>
-      </c>
       <c r="G348" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
@@ -10322,13 +10323,13 @@
         <v>6</v>
       </c>
       <c r="E349" t="s">
+        <v>207</v>
+      </c>
+      <c r="F349" t="s">
         <v>208</v>
       </c>
-      <c r="F349" t="s">
-        <v>209</v>
-      </c>
       <c r="G349" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
@@ -10345,7 +10346,7 @@
         <v>7</v>
       </c>
       <c r="E350" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
@@ -10362,13 +10363,13 @@
         <v>7</v>
       </c>
       <c r="E351" t="s">
+        <v>209</v>
+      </c>
+      <c r="F351" t="s">
         <v>210</v>
       </c>
-      <c r="F351" t="s">
-        <v>211</v>
-      </c>
       <c r="G351" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
@@ -10385,13 +10386,13 @@
         <v>7</v>
       </c>
       <c r="E352" t="s">
+        <v>209</v>
+      </c>
+      <c r="F352" t="s">
         <v>210</v>
       </c>
-      <c r="F352" t="s">
+      <c r="G352" t="s">
         <v>211</v>
-      </c>
-      <c r="G352" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
@@ -10408,7 +10409,7 @@
         <v>8</v>
       </c>
       <c r="E353" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
@@ -10425,13 +10426,13 @@
         <v>8</v>
       </c>
       <c r="E354" t="s">
+        <v>212</v>
+      </c>
+      <c r="F354" t="s">
         <v>213</v>
       </c>
-      <c r="F354" t="s">
-        <v>214</v>
-      </c>
       <c r="G354" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
@@ -10448,13 +10449,13 @@
         <v>8</v>
       </c>
       <c r="E355" t="s">
+        <v>212</v>
+      </c>
+      <c r="F355" t="s">
         <v>213</v>
       </c>
-      <c r="F355" t="s">
-        <v>214</v>
-      </c>
       <c r="G355" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
@@ -10471,7 +10472,7 @@
         <v>9</v>
       </c>
       <c r="E356" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
@@ -10488,13 +10489,13 @@
         <v>9</v>
       </c>
       <c r="E357" t="s">
+        <v>214</v>
+      </c>
+      <c r="F357" t="s">
         <v>215</v>
       </c>
-      <c r="F357" t="s">
-        <v>216</v>
-      </c>
       <c r="G357" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
@@ -10511,13 +10512,13 @@
         <v>9</v>
       </c>
       <c r="E358" t="s">
+        <v>214</v>
+      </c>
+      <c r="F358" t="s">
         <v>215</v>
       </c>
-      <c r="F358" t="s">
-        <v>216</v>
-      </c>
       <c r="G358" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
@@ -10534,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="E359" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
@@ -10551,13 +10552,13 @@
         <v>10</v>
       </c>
       <c r="E360" t="s">
+        <v>216</v>
+      </c>
+      <c r="F360" t="s">
         <v>217</v>
       </c>
-      <c r="F360" t="s">
-        <v>218</v>
-      </c>
       <c r="G360" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
@@ -10574,13 +10575,13 @@
         <v>10</v>
       </c>
       <c r="E361" t="s">
+        <v>216</v>
+      </c>
+      <c r="F361" t="s">
         <v>217</v>
       </c>
-      <c r="F361" t="s">
-        <v>218</v>
-      </c>
       <c r="G361" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
@@ -10597,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="E362" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
@@ -10614,13 +10615,13 @@
         <v>1</v>
       </c>
       <c r="E363" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F363" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G363" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
@@ -10637,13 +10638,13 @@
         <v>1</v>
       </c>
       <c r="E364" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F364" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G364" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
@@ -10660,7 +10661,7 @@
         <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
@@ -10677,13 +10678,13 @@
         <v>2</v>
       </c>
       <c r="E366" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F366" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G366" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
@@ -10700,13 +10701,13 @@
         <v>2</v>
       </c>
       <c r="E367" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G367" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
@@ -10723,7 +10724,7 @@
         <v>3</v>
       </c>
       <c r="E368" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
@@ -10740,13 +10741,13 @@
         <v>3</v>
       </c>
       <c r="E369" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F369" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G369" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
@@ -10763,13 +10764,13 @@
         <v>3</v>
       </c>
       <c r="E370" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F370" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G370" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
@@ -10786,7 +10787,7 @@
         <v>4</v>
       </c>
       <c r="E371" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
@@ -10803,13 +10804,13 @@
         <v>4</v>
       </c>
       <c r="E372" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F372" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G372" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
@@ -10826,13 +10827,13 @@
         <v>4</v>
       </c>
       <c r="E373" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F373" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G373" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
@@ -10849,7 +10850,7 @@
         <v>5</v>
       </c>
       <c r="E374" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
@@ -10866,13 +10867,13 @@
         <v>5</v>
       </c>
       <c r="E375" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F375" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G375" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
@@ -10889,13 +10890,13 @@
         <v>5</v>
       </c>
       <c r="E376" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F376" t="s">
+        <v>222</v>
+      </c>
+      <c r="G376" t="s">
         <v>223</v>
-      </c>
-      <c r="G376" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
@@ -10912,7 +10913,7 @@
         <v>6</v>
       </c>
       <c r="E377" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
@@ -10929,13 +10930,13 @@
         <v>6</v>
       </c>
       <c r="E378" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F378" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G378" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
@@ -10952,13 +10953,13 @@
         <v>6</v>
       </c>
       <c r="E379" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F379" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G379" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
@@ -10975,7 +10976,7 @@
         <v>7</v>
       </c>
       <c r="E380" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,13 +10993,13 @@
         <v>7</v>
       </c>
       <c r="E381" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F381" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G381" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,13 +11016,13 @@
         <v>7</v>
       </c>
       <c r="E382" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F382" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G382" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,7 +11039,7 @@
         <v>8</v>
       </c>
       <c r="E383" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
@@ -11055,13 +11056,13 @@
         <v>8</v>
       </c>
       <c r="E384" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F384" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G384" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
@@ -11078,13 +11079,13 @@
         <v>8</v>
       </c>
       <c r="E385" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F385" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G385" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
@@ -11101,7 +11102,7 @@
         <v>9</v>
       </c>
       <c r="E386" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
@@ -11118,13 +11119,13 @@
         <v>9</v>
       </c>
       <c r="E387" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F387" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G387" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
@@ -11141,13 +11142,13 @@
         <v>9</v>
       </c>
       <c r="E388" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F388" t="s">
+        <v>227</v>
+      </c>
+      <c r="G388" t="s">
         <v>228</v>
-      </c>
-      <c r="G388" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
@@ -11164,7 +11165,7 @@
         <v>10</v>
       </c>
       <c r="E389" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
@@ -11181,13 +11182,13 @@
         <v>10</v>
       </c>
       <c r="E390" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F390" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G390" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
@@ -11204,13 +11205,13 @@
         <v>10</v>
       </c>
       <c r="E391" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F391" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G391" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
@@ -11227,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="E392" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
@@ -11244,13 +11245,13 @@
         <v>1</v>
       </c>
       <c r="E393" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F393" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G393" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
@@ -11267,13 +11268,13 @@
         <v>1</v>
       </c>
       <c r="E394" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F394" t="s">
+        <v>230</v>
+      </c>
+      <c r="G394" t="s">
         <v>231</v>
-      </c>
-      <c r="G394" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
@@ -11290,7 +11291,7 @@
         <v>2</v>
       </c>
       <c r="E395" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
@@ -11307,13 +11308,13 @@
         <v>2</v>
       </c>
       <c r="E396" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F396" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G396" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
@@ -11330,13 +11331,13 @@
         <v>2</v>
       </c>
       <c r="E397" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F397" t="s">
+        <v>232</v>
+      </c>
+      <c r="G397" t="s">
         <v>233</v>
-      </c>
-      <c r="G397" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
@@ -11353,7 +11354,7 @@
         <v>3</v>
       </c>
       <c r="E398" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
@@ -11370,13 +11371,13 @@
         <v>3</v>
       </c>
       <c r="E399" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F399" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G399" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
@@ -11393,13 +11394,13 @@
         <v>3</v>
       </c>
       <c r="E400" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F400" t="s">
+        <v>234</v>
+      </c>
+      <c r="G400" t="s">
         <v>235</v>
-      </c>
-      <c r="G400" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.3">
@@ -11416,7 +11417,7 @@
         <v>4</v>
       </c>
       <c r="E401" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.3">
@@ -11433,13 +11434,13 @@
         <v>4</v>
       </c>
       <c r="E402" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F402" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G402" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.3">
@@ -11456,13 +11457,13 @@
         <v>4</v>
       </c>
       <c r="E403" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F403" t="s">
+        <v>236</v>
+      </c>
+      <c r="G403" t="s">
         <v>237</v>
-      </c>
-      <c r="G403" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.3">
@@ -11479,7 +11480,7 @@
         <v>5</v>
       </c>
       <c r="E404" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.3">
@@ -11496,13 +11497,13 @@
         <v>5</v>
       </c>
       <c r="E405" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F405" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G405" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.3">
@@ -11519,13 +11520,13 @@
         <v>5</v>
       </c>
       <c r="E406" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F406" t="s">
+        <v>238</v>
+      </c>
+      <c r="G406" t="s">
         <v>239</v>
-      </c>
-      <c r="G406" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.3">
@@ -11542,7 +11543,7 @@
         <v>6</v>
       </c>
       <c r="E407" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.3">
@@ -11559,13 +11560,13 @@
         <v>6</v>
       </c>
       <c r="E408" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F408" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G408" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.3">
@@ -11582,13 +11583,13 @@
         <v>6</v>
       </c>
       <c r="E409" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F409" t="s">
+        <v>240</v>
+      </c>
+      <c r="G409" t="s">
         <v>241</v>
-      </c>
-      <c r="G409" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.3">
@@ -11605,7 +11606,7 @@
         <v>7</v>
       </c>
       <c r="E410" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.3">
@@ -11622,13 +11623,13 @@
         <v>7</v>
       </c>
       <c r="E411" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F411" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G411" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.3">
@@ -11645,13 +11646,13 @@
         <v>7</v>
       </c>
       <c r="E412" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F412" t="s">
+        <v>242</v>
+      </c>
+      <c r="G412" t="s">
         <v>243</v>
-      </c>
-      <c r="G412" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.3">
@@ -11668,7 +11669,7 @@
         <v>8</v>
       </c>
       <c r="E413" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.3">
@@ -11685,13 +11686,13 @@
         <v>8</v>
       </c>
       <c r="E414" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F414" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G414" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.3">
@@ -11708,13 +11709,13 @@
         <v>8</v>
       </c>
       <c r="E415" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F415" t="s">
+        <v>244</v>
+      </c>
+      <c r="G415" t="s">
         <v>245</v>
-      </c>
-      <c r="G415" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
@@ -11731,7 +11732,7 @@
         <v>9</v>
       </c>
       <c r="E416" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
@@ -11748,13 +11749,13 @@
         <v>9</v>
       </c>
       <c r="E417" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F417" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G417" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
@@ -11771,13 +11772,13 @@
         <v>9</v>
       </c>
       <c r="E418" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F418" t="s">
+        <v>246</v>
+      </c>
+      <c r="G418" t="s">
         <v>247</v>
-      </c>
-      <c r="G418" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
@@ -11794,7 +11795,7 @@
         <v>10</v>
       </c>
       <c r="E419" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
@@ -11811,13 +11812,13 @@
         <v>10</v>
       </c>
       <c r="E420" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F420" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G420" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
@@ -11834,13 +11835,13 @@
         <v>10</v>
       </c>
       <c r="E421" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F421" t="s">
+        <v>248</v>
+      </c>
+      <c r="G421" t="s">
         <v>249</v>
-      </c>
-      <c r="G421" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
@@ -11857,7 +11858,7 @@
         <v>1</v>
       </c>
       <c r="E422" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
@@ -11874,13 +11875,13 @@
         <v>1</v>
       </c>
       <c r="E423" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F423" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G423" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
@@ -11897,13 +11898,13 @@
         <v>1</v>
       </c>
       <c r="E424" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F424" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G424" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
@@ -11920,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="E425" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
@@ -11937,13 +11938,13 @@
         <v>2</v>
       </c>
       <c r="E426" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F426" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G426" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
@@ -11960,13 +11961,13 @@
         <v>2</v>
       </c>
       <c r="E427" t="s">
+        <v>251</v>
+      </c>
+      <c r="F427" t="s">
         <v>252</v>
       </c>
-      <c r="F427" t="s">
-        <v>253</v>
-      </c>
       <c r="G427" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
@@ -11983,7 +11984,7 @@
         <v>3</v>
       </c>
       <c r="E428" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
@@ -12000,13 +12001,13 @@
         <v>3</v>
       </c>
       <c r="E429" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F429" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G429" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
@@ -12023,13 +12024,13 @@
         <v>3</v>
       </c>
       <c r="E430" t="s">
+        <v>253</v>
+      </c>
+      <c r="F430" t="s">
         <v>254</v>
       </c>
-      <c r="F430" t="s">
-        <v>255</v>
-      </c>
       <c r="G430" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
@@ -12046,7 +12047,7 @@
         <v>4</v>
       </c>
       <c r="E431" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
@@ -12063,13 +12064,13 @@
         <v>4</v>
       </c>
       <c r="E432" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F432" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G432" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
@@ -12086,13 +12087,13 @@
         <v>4</v>
       </c>
       <c r="E433" t="s">
+        <v>255</v>
+      </c>
+      <c r="F433" t="s">
         <v>256</v>
       </c>
-      <c r="F433" t="s">
-        <v>257</v>
-      </c>
       <c r="G433" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
@@ -12109,7 +12110,7 @@
         <v>5</v>
       </c>
       <c r="E434" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
@@ -12126,13 +12127,13 @@
         <v>5</v>
       </c>
       <c r="E435" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F435" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G435" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
@@ -12149,13 +12150,13 @@
         <v>5</v>
       </c>
       <c r="E436" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F436" t="s">
+        <v>257</v>
+      </c>
+      <c r="G436" t="s">
         <v>258</v>
-      </c>
-      <c r="G436" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
@@ -12172,7 +12173,7 @@
         <v>6</v>
       </c>
       <c r="E437" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
@@ -12189,13 +12190,13 @@
         <v>6</v>
       </c>
       <c r="E438" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F438" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G438" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
@@ -12212,13 +12213,13 @@
         <v>6</v>
       </c>
       <c r="E439" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F439" t="s">
+        <v>259</v>
+      </c>
+      <c r="G439" t="s">
         <v>260</v>
-      </c>
-      <c r="G439" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
@@ -12235,7 +12236,7 @@
         <v>7</v>
       </c>
       <c r="E440" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
@@ -12252,13 +12253,13 @@
         <v>7</v>
       </c>
       <c r="E441" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F441" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G441" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
@@ -12275,13 +12276,13 @@
         <v>7</v>
       </c>
       <c r="E442" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F442" t="s">
+        <v>261</v>
+      </c>
+      <c r="G442" t="s">
         <v>262</v>
-      </c>
-      <c r="G442" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
@@ -12298,7 +12299,7 @@
         <v>8</v>
       </c>
       <c r="E443" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
@@ -12315,13 +12316,13 @@
         <v>8</v>
       </c>
       <c r="E444" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F444" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G444" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
@@ -12338,13 +12339,13 @@
         <v>8</v>
       </c>
       <c r="E445" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F445" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G445" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
@@ -12361,7 +12362,7 @@
         <v>9</v>
       </c>
       <c r="E446" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
@@ -12378,13 +12379,13 @@
         <v>9</v>
       </c>
       <c r="E447" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F447" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G447" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
@@ -12401,13 +12402,13 @@
         <v>9</v>
       </c>
       <c r="E448" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F448" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G448" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
@@ -12424,7 +12425,7 @@
         <v>10</v>
       </c>
       <c r="E449" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
@@ -12441,13 +12442,13 @@
         <v>10</v>
       </c>
       <c r="E450" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F450" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G450" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
@@ -12464,13 +12465,13 @@
         <v>10</v>
       </c>
       <c r="E451" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F451" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G451" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="452" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -12487,7 +12488,7 @@
         <v>1</v>
       </c>
       <c r="E452" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F452"/>
       <c r="G452"/>
@@ -12506,13 +12507,13 @@
         <v>1</v>
       </c>
       <c r="E453" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F453" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G453" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
@@ -12529,13 +12530,13 @@
         <v>1</v>
       </c>
       <c r="E454" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F454" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G454" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
@@ -12552,7 +12553,7 @@
         <v>2</v>
       </c>
       <c r="E455" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
@@ -12569,13 +12570,13 @@
         <v>2</v>
       </c>
       <c r="E456" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F456" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G456" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
@@ -12592,13 +12593,13 @@
         <v>2</v>
       </c>
       <c r="E457" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F457" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G457" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
@@ -12615,7 +12616,7 @@
         <v>3</v>
       </c>
       <c r="E458" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
@@ -12632,13 +12633,13 @@
         <v>3</v>
       </c>
       <c r="E459" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F459" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G459" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
@@ -12655,13 +12656,13 @@
         <v>3</v>
       </c>
       <c r="E460" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F460" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G460" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
@@ -12678,7 +12679,7 @@
         <v>4</v>
       </c>
       <c r="E461" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
@@ -12695,13 +12696,13 @@
         <v>4</v>
       </c>
       <c r="E462" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F462" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G462" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
@@ -12718,13 +12719,13 @@
         <v>4</v>
       </c>
       <c r="E463" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F463" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G463" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
@@ -12741,7 +12742,7 @@
         <v>5</v>
       </c>
       <c r="E464" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.3">
@@ -12758,13 +12759,13 @@
         <v>5</v>
       </c>
       <c r="E465" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F465" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G465" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
@@ -12781,13 +12782,13 @@
         <v>5</v>
       </c>
       <c r="E466" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F466" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G466" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
@@ -12804,7 +12805,7 @@
         <v>6</v>
       </c>
       <c r="E467" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
@@ -12821,13 +12822,13 @@
         <v>6</v>
       </c>
       <c r="E468" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F468" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G468" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
@@ -12844,13 +12845,13 @@
         <v>6</v>
       </c>
       <c r="E469" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F469" t="s">
+        <v>271</v>
+      </c>
+      <c r="G469" t="s">
         <v>272</v>
-      </c>
-      <c r="G469" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
@@ -12867,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="E470" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
@@ -12884,13 +12885,13 @@
         <v>7</v>
       </c>
       <c r="E471" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F471" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G471" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
@@ -12907,13 +12908,13 @@
         <v>7</v>
       </c>
       <c r="E472" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F472" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G472" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
@@ -12930,7 +12931,7 @@
         <v>8</v>
       </c>
       <c r="E473" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
@@ -12947,13 +12948,13 @@
         <v>8</v>
       </c>
       <c r="E474" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F474" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G474" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
@@ -12970,13 +12971,13 @@
         <v>8</v>
       </c>
       <c r="E475" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F475" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G475" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
@@ -12993,7 +12994,7 @@
         <v>9</v>
       </c>
       <c r="E476" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
@@ -13010,13 +13011,13 @@
         <v>9</v>
       </c>
       <c r="E477" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F477" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G477" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
@@ -13033,13 +13034,13 @@
         <v>9</v>
       </c>
       <c r="E478" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F478" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G478" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
@@ -13056,7 +13057,7 @@
         <v>10</v>
       </c>
       <c r="E479" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
@@ -13073,13 +13074,13 @@
         <v>10</v>
       </c>
       <c r="E480" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F480" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G480" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
@@ -13096,13 +13097,13 @@
         <v>10</v>
       </c>
       <c r="E481" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F481" t="s">
+        <v>276</v>
+      </c>
+      <c r="G481" t="s">
         <v>277</v>
-      </c>
-      <c r="G481" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
@@ -13119,7 +13120,7 @@
         <v>1</v>
       </c>
       <c r="E482" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
@@ -13136,13 +13137,13 @@
         <v>1</v>
       </c>
       <c r="E483" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F483" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G483" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
@@ -13159,13 +13160,13 @@
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F484" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G484" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
@@ -13182,7 +13183,7 @@
         <v>2</v>
       </c>
       <c r="E485" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
@@ -13199,13 +13200,13 @@
         <v>2</v>
       </c>
       <c r="E486" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F486" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G486" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
@@ -13222,13 +13223,13 @@
         <v>2</v>
       </c>
       <c r="E487" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F487" t="s">
+        <v>279</v>
+      </c>
+      <c r="G487" t="s">
         <v>280</v>
-      </c>
-      <c r="G487" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
@@ -13245,7 +13246,7 @@
         <v>3</v>
       </c>
       <c r="E488" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
@@ -13262,13 +13263,13 @@
         <v>3</v>
       </c>
       <c r="E489" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F489" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G489" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
@@ -13285,13 +13286,13 @@
         <v>3</v>
       </c>
       <c r="E490" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F490" t="s">
+        <v>281</v>
+      </c>
+      <c r="G490" t="s">
         <v>282</v>
-      </c>
-      <c r="G490" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
@@ -13308,7 +13309,7 @@
         <v>4</v>
       </c>
       <c r="E491" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
@@ -13325,13 +13326,13 @@
         <v>4</v>
       </c>
       <c r="E492" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F492" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G492" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
@@ -13348,13 +13349,13 @@
         <v>4</v>
       </c>
       <c r="E493" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F493" t="s">
+        <v>283</v>
+      </c>
+      <c r="G493" t="s">
         <v>284</v>
-      </c>
-      <c r="G493" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
@@ -13371,7 +13372,7 @@
         <v>5</v>
       </c>
       <c r="E494" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
@@ -13388,13 +13389,13 @@
         <v>5</v>
       </c>
       <c r="E495" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F495" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G495" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
@@ -13411,13 +13412,13 @@
         <v>5</v>
       </c>
       <c r="E496" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F496" t="s">
+        <v>285</v>
+      </c>
+      <c r="G496" t="s">
         <v>286</v>
-      </c>
-      <c r="G496" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
@@ -13434,7 +13435,7 @@
         <v>6</v>
       </c>
       <c r="E497" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
@@ -13451,13 +13452,13 @@
         <v>6</v>
       </c>
       <c r="E498" t="s">
+        <v>287</v>
+      </c>
+      <c r="F498" t="s">
         <v>288</v>
       </c>
-      <c r="F498" t="s">
-        <v>289</v>
-      </c>
       <c r="G498" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
@@ -13474,13 +13475,13 @@
         <v>6</v>
       </c>
       <c r="E499" t="s">
+        <v>287</v>
+      </c>
+      <c r="F499" t="s">
         <v>288</v>
       </c>
-      <c r="F499" t="s">
+      <c r="G499" t="s">
         <v>289</v>
-      </c>
-      <c r="G499" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
@@ -13497,7 +13498,7 @@
         <v>7</v>
       </c>
       <c r="E500" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
@@ -13514,13 +13515,13 @@
         <v>7</v>
       </c>
       <c r="E501" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F501" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G501" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
@@ -13537,13 +13538,13 @@
         <v>7</v>
       </c>
       <c r="E502" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F502" t="s">
+        <v>290</v>
+      </c>
+      <c r="G502" t="s">
         <v>291</v>
-      </c>
-      <c r="G502" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
@@ -13560,7 +13561,7 @@
         <v>8</v>
       </c>
       <c r="E503" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
@@ -13577,13 +13578,13 @@
         <v>8</v>
       </c>
       <c r="E504" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F504" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G504" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
@@ -13600,13 +13601,13 @@
         <v>8</v>
       </c>
       <c r="E505" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F505" t="s">
+        <v>292</v>
+      </c>
+      <c r="G505" t="s">
         <v>293</v>
-      </c>
-      <c r="G505" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
@@ -13623,7 +13624,7 @@
         <v>9</v>
       </c>
       <c r="E506" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -13640,10 +13641,10 @@
         <v>9</v>
       </c>
       <c r="E507" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F507" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
@@ -13660,13 +13661,13 @@
         <v>9</v>
       </c>
       <c r="E508" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F508" t="s">
+        <v>294</v>
+      </c>
+      <c r="G508" t="s">
         <v>295</v>
-      </c>
-      <c r="G508" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
@@ -13683,7 +13684,7 @@
         <v>10</v>
       </c>
       <c r="E509" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -13700,13 +13701,13 @@
         <v>10</v>
       </c>
       <c r="E510" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F510" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G510" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
@@ -13723,13 +13724,13 @@
         <v>10</v>
       </c>
       <c r="E511" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F511" t="s">
+        <v>296</v>
+      </c>
+      <c r="G511" t="s">
         <v>297</v>
-      </c>
-      <c r="G511" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
@@ -13746,7 +13747,7 @@
         <v>1</v>
       </c>
       <c r="E512" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -13763,13 +13764,13 @@
         <v>1</v>
       </c>
       <c r="E513" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F513" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G513" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
@@ -13786,13 +13787,13 @@
         <v>1</v>
       </c>
       <c r="E514" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F514" t="s">
+        <v>298</v>
+      </c>
+      <c r="G514" t="s">
         <v>299</v>
-      </c>
-      <c r="G514" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
@@ -13809,7 +13810,7 @@
         <v>2</v>
       </c>
       <c r="E515" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -13826,13 +13827,13 @@
         <v>2</v>
       </c>
       <c r="E516" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F516" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G516" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
@@ -13849,13 +13850,13 @@
         <v>2</v>
       </c>
       <c r="E517" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F517" t="s">
+        <v>300</v>
+      </c>
+      <c r="G517" t="s">
         <v>301</v>
-      </c>
-      <c r="G517" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -13872,7 +13873,7 @@
         <v>3</v>
       </c>
       <c r="E518" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -13889,13 +13890,13 @@
         <v>3</v>
       </c>
       <c r="E519" t="s">
+        <v>302</v>
+      </c>
+      <c r="F519" t="s">
         <v>303</v>
       </c>
-      <c r="F519" t="s">
-        <v>304</v>
-      </c>
       <c r="G519" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
@@ -13912,13 +13913,13 @@
         <v>3</v>
       </c>
       <c r="E520" t="s">
+        <v>302</v>
+      </c>
+      <c r="F520" t="s">
         <v>303</v>
       </c>
-      <c r="F520" t="s">
+      <c r="G520" t="s">
         <v>304</v>
-      </c>
-      <c r="G520" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
@@ -13935,7 +13936,7 @@
         <v>4</v>
       </c>
       <c r="E521" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -13952,13 +13953,13 @@
         <v>4</v>
       </c>
       <c r="E522" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F522" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G522" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
@@ -13975,13 +13976,13 @@
         <v>4</v>
       </c>
       <c r="E523" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F523" t="s">
+        <v>305</v>
+      </c>
+      <c r="G523" t="s">
         <v>306</v>
-      </c>
-      <c r="G523" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
@@ -13998,7 +13999,7 @@
         <v>5</v>
       </c>
       <c r="E524" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -14015,13 +14016,13 @@
         <v>5</v>
       </c>
       <c r="E525" t="s">
+        <v>307</v>
+      </c>
+      <c r="F525" t="s">
         <v>308</v>
       </c>
-      <c r="F525" t="s">
-        <v>309</v>
-      </c>
       <c r="G525" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
@@ -14038,13 +14039,13 @@
         <v>5</v>
       </c>
       <c r="E526" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F526" t="s">
+        <v>308</v>
+      </c>
+      <c r="G526" t="s">
         <v>309</v>
-      </c>
-      <c r="G526" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
@@ -14061,7 +14062,7 @@
         <v>6</v>
       </c>
       <c r="E527" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -14078,13 +14079,13 @@
         <v>6</v>
       </c>
       <c r="E528" t="s">
+        <v>310</v>
+      </c>
+      <c r="F528" t="s">
         <v>311</v>
       </c>
-      <c r="F528" t="s">
-        <v>312</v>
-      </c>
       <c r="G528" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
@@ -14101,13 +14102,13 @@
         <v>6</v>
       </c>
       <c r="E529" t="s">
+        <v>310</v>
+      </c>
+      <c r="F529" t="s">
         <v>311</v>
       </c>
-      <c r="F529" t="s">
+      <c r="G529" t="s">
         <v>312</v>
-      </c>
-      <c r="G529" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
@@ -14124,7 +14125,7 @@
         <v>7</v>
       </c>
       <c r="E530" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
@@ -14141,13 +14142,13 @@
         <v>7</v>
       </c>
       <c r="E531" t="s">
+        <v>313</v>
+      </c>
+      <c r="F531" t="s">
         <v>314</v>
       </c>
-      <c r="F531" t="s">
-        <v>315</v>
-      </c>
       <c r="G531" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
@@ -14164,13 +14165,13 @@
         <v>7</v>
       </c>
       <c r="E532" t="s">
+        <v>313</v>
+      </c>
+      <c r="F532" t="s">
         <v>314</v>
       </c>
-      <c r="F532" t="s">
+      <c r="G532" t="s">
         <v>315</v>
-      </c>
-      <c r="G532" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
@@ -14187,7 +14188,7 @@
         <v>8</v>
       </c>
       <c r="E533" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
@@ -14204,13 +14205,13 @@
         <v>8</v>
       </c>
       <c r="E534" t="s">
+        <v>316</v>
+      </c>
+      <c r="F534" t="s">
         <v>317</v>
       </c>
-      <c r="F534" t="s">
-        <v>318</v>
-      </c>
       <c r="G534" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
@@ -14227,13 +14228,13 @@
         <v>8</v>
       </c>
       <c r="E535" t="s">
+        <v>316</v>
+      </c>
+      <c r="F535" t="s">
         <v>317</v>
       </c>
-      <c r="F535" t="s">
+      <c r="G535" t="s">
         <v>318</v>
-      </c>
-      <c r="G535" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
@@ -14250,7 +14251,7 @@
         <v>9</v>
       </c>
       <c r="E536" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
@@ -14267,13 +14268,13 @@
         <v>9</v>
       </c>
       <c r="E537" t="s">
+        <v>319</v>
+      </c>
+      <c r="F537" t="s">
         <v>320</v>
       </c>
-      <c r="F537" t="s">
-        <v>321</v>
-      </c>
       <c r="G537" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
@@ -14290,13 +14291,13 @@
         <v>9</v>
       </c>
       <c r="E538" t="s">
+        <v>319</v>
+      </c>
+      <c r="F538" t="s">
         <v>320</v>
       </c>
-      <c r="F538" t="s">
+      <c r="G538" t="s">
         <v>321</v>
-      </c>
-      <c r="G538" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
@@ -14313,7 +14314,7 @@
         <v>10</v>
       </c>
       <c r="E539" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
@@ -14330,13 +14331,13 @@
         <v>10</v>
       </c>
       <c r="E540" t="s">
+        <v>322</v>
+      </c>
+      <c r="F540" t="s">
         <v>323</v>
       </c>
-      <c r="F540" t="s">
-        <v>324</v>
-      </c>
       <c r="G540" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
@@ -14353,13 +14354,13 @@
         <v>10</v>
       </c>
       <c r="E541" t="s">
+        <v>322</v>
+      </c>
+      <c r="F541" t="s">
         <v>323</v>
       </c>
-      <c r="F541" t="s">
+      <c r="G541" t="s">
         <v>324</v>
-      </c>
-      <c r="G541" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
@@ -14367,7 +14368,7 @@
         <v>39</v>
       </c>
       <c r="B542" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C542" t="s">
         <v>6</v>
@@ -14376,7 +14377,7 @@
         <v>1</v>
       </c>
       <c r="E542" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
@@ -14384,7 +14385,7 @@
         <v>39</v>
       </c>
       <c r="B543" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C543" t="s">
         <v>7</v>
@@ -14393,13 +14394,13 @@
         <v>1</v>
       </c>
       <c r="E543" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F543" t="s">
+        <v>780</v>
+      </c>
+      <c r="G543" t="s">
         <v>781</v>
-      </c>
-      <c r="G543" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.3">
@@ -14407,7 +14408,7 @@
         <v>39</v>
       </c>
       <c r="B544" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C544" t="s">
         <v>8</v>
@@ -14416,13 +14417,13 @@
         <v>1</v>
       </c>
       <c r="E544" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F544" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G544" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
@@ -14430,7 +14431,7 @@
         <v>39</v>
       </c>
       <c r="B545" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C545" t="s">
         <v>6</v>
@@ -14439,7 +14440,7 @@
         <v>2</v>
       </c>
       <c r="E545" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
@@ -14447,7 +14448,7 @@
         <v>39</v>
       </c>
       <c r="B546" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C546" t="s">
         <v>7</v>
@@ -14456,13 +14457,13 @@
         <v>2</v>
       </c>
       <c r="E546" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F546" t="s">
+        <v>783</v>
+      </c>
+      <c r="G546" t="s">
         <v>784</v>
-      </c>
-      <c r="G546" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -14470,7 +14471,7 @@
         <v>39</v>
       </c>
       <c r="B547" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C547" t="s">
         <v>8</v>
@@ -14479,13 +14480,13 @@
         <v>2</v>
       </c>
       <c r="E547" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F547" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G547" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
@@ -14493,7 +14494,7 @@
         <v>39</v>
       </c>
       <c r="B548" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C548" t="s">
         <v>6</v>
@@ -14502,7 +14503,7 @@
         <v>3</v>
       </c>
       <c r="E548" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
@@ -14510,7 +14511,7 @@
         <v>39</v>
       </c>
       <c r="B549" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C549" t="s">
         <v>7</v>
@@ -14519,13 +14520,13 @@
         <v>3</v>
       </c>
       <c r="E549" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F549" t="s">
+        <v>786</v>
+      </c>
+      <c r="G549" t="s">
         <v>787</v>
-      </c>
-      <c r="G549" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
@@ -14533,7 +14534,7 @@
         <v>39</v>
       </c>
       <c r="B550" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C550" t="s">
         <v>8</v>
@@ -14542,13 +14543,13 @@
         <v>3</v>
       </c>
       <c r="E550" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F550" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G550" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
@@ -14556,7 +14557,7 @@
         <v>39</v>
       </c>
       <c r="B551" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C551" t="s">
         <v>6</v>
@@ -14565,7 +14566,7 @@
         <v>4</v>
       </c>
       <c r="E551" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
@@ -14573,7 +14574,7 @@
         <v>39</v>
       </c>
       <c r="B552" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C552" t="s">
         <v>7</v>
@@ -14582,13 +14583,13 @@
         <v>4</v>
       </c>
       <c r="E552" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F552" t="s">
+        <v>789</v>
+      </c>
+      <c r="G552" t="s">
         <v>790</v>
-      </c>
-      <c r="G552" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
@@ -14596,7 +14597,7 @@
         <v>39</v>
       </c>
       <c r="B553" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C553" t="s">
         <v>8</v>
@@ -14605,13 +14606,13 @@
         <v>4</v>
       </c>
       <c r="E553" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F553" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G553" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
@@ -14619,7 +14620,7 @@
         <v>39</v>
       </c>
       <c r="B554" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C554" t="s">
         <v>6</v>
@@ -14628,7 +14629,7 @@
         <v>5</v>
       </c>
       <c r="E554" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
@@ -14636,7 +14637,7 @@
         <v>39</v>
       </c>
       <c r="B555" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C555" t="s">
         <v>7</v>
@@ -14645,13 +14646,13 @@
         <v>5</v>
       </c>
       <c r="E555" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F555" t="s">
+        <v>792</v>
+      </c>
+      <c r="G555" t="s">
         <v>793</v>
-      </c>
-      <c r="G555" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
@@ -14659,7 +14660,7 @@
         <v>39</v>
       </c>
       <c r="B556" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C556" t="s">
         <v>8</v>
@@ -14668,13 +14669,13 @@
         <v>5</v>
       </c>
       <c r="E556" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F556" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G556" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
@@ -14682,7 +14683,7 @@
         <v>39</v>
       </c>
       <c r="B557" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C557" t="s">
         <v>6</v>
@@ -14691,7 +14692,7 @@
         <v>6</v>
       </c>
       <c r="E557" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
@@ -14699,7 +14700,7 @@
         <v>39</v>
       </c>
       <c r="B558" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C558" t="s">
         <v>7</v>
@@ -14708,13 +14709,13 @@
         <v>6</v>
       </c>
       <c r="E558" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F558" t="s">
+        <v>795</v>
+      </c>
+      <c r="G558" t="s">
         <v>796</v>
-      </c>
-      <c r="G558" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
@@ -14722,7 +14723,7 @@
         <v>39</v>
       </c>
       <c r="B559" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C559" t="s">
         <v>8</v>
@@ -14731,13 +14732,13 @@
         <v>6</v>
       </c>
       <c r="E559" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F559" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G559" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
@@ -14745,7 +14746,7 @@
         <v>39</v>
       </c>
       <c r="B560" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C560" t="s">
         <v>6</v>
@@ -14754,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="E560" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
@@ -14762,7 +14763,7 @@
         <v>39</v>
       </c>
       <c r="B561" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C561" t="s">
         <v>7</v>
@@ -14771,13 +14772,13 @@
         <v>7</v>
       </c>
       <c r="E561" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F561" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G561" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
@@ -14785,7 +14786,7 @@
         <v>39</v>
       </c>
       <c r="B562" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C562" t="s">
         <v>8</v>
@@ -14794,13 +14795,13 @@
         <v>7</v>
       </c>
       <c r="E562" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F562" t="s">
+        <v>798</v>
+      </c>
+      <c r="G562" t="s">
         <v>799</v>
-      </c>
-      <c r="G562" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
@@ -14808,7 +14809,7 @@
         <v>39</v>
       </c>
       <c r="B563" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C563" t="s">
         <v>6</v>
@@ -14817,7 +14818,7 @@
         <v>8</v>
       </c>
       <c r="E563" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
@@ -14825,7 +14826,7 @@
         <v>39</v>
       </c>
       <c r="B564" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C564" t="s">
         <v>7</v>
@@ -14834,13 +14835,13 @@
         <v>8</v>
       </c>
       <c r="E564" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F564" t="s">
+        <v>800</v>
+      </c>
+      <c r="G564" t="s">
         <v>801</v>
-      </c>
-      <c r="G564" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
@@ -14848,7 +14849,7 @@
         <v>39</v>
       </c>
       <c r="B565" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C565" t="s">
         <v>8</v>
@@ -14857,13 +14858,13 @@
         <v>8</v>
       </c>
       <c r="E565" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F565" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G565" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
@@ -14871,7 +14872,7 @@
         <v>39</v>
       </c>
       <c r="B566" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C566" t="s">
         <v>6</v>
@@ -14880,7 +14881,7 @@
         <v>9</v>
       </c>
       <c r="E566" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
@@ -14888,7 +14889,7 @@
         <v>39</v>
       </c>
       <c r="B567" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C567" t="s">
         <v>7</v>
@@ -14897,13 +14898,13 @@
         <v>9</v>
       </c>
       <c r="E567" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F567" t="s">
+        <v>803</v>
+      </c>
+      <c r="G567" t="s">
         <v>804</v>
-      </c>
-      <c r="G567" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
@@ -14911,7 +14912,7 @@
         <v>39</v>
       </c>
       <c r="B568" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C568" t="s">
         <v>8</v>
@@ -14920,13 +14921,13 @@
         <v>9</v>
       </c>
       <c r="E568" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F568" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G568" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
@@ -14934,7 +14935,7 @@
         <v>39</v>
       </c>
       <c r="B569" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C569" t="s">
         <v>6</v>
@@ -14943,7 +14944,7 @@
         <v>10</v>
       </c>
       <c r="E569" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
@@ -14951,7 +14952,7 @@
         <v>39</v>
       </c>
       <c r="B570" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C570" t="s">
         <v>7</v>
@@ -14960,13 +14961,13 @@
         <v>10</v>
       </c>
       <c r="E570" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F570" t="s">
+        <v>806</v>
+      </c>
+      <c r="G570" t="s">
         <v>807</v>
-      </c>
-      <c r="G570" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
@@ -14974,7 +14975,7 @@
         <v>39</v>
       </c>
       <c r="B571" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C571" t="s">
         <v>8</v>
@@ -14983,13 +14984,13 @@
         <v>10</v>
       </c>
       <c r="E571" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F571" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G571" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
@@ -14997,7 +14998,7 @@
         <v>40</v>
       </c>
       <c r="B572" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C572" t="s">
         <v>6</v>
@@ -15006,7 +15007,7 @@
         <v>1</v>
       </c>
       <c r="E572" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
@@ -15014,7 +15015,7 @@
         <v>40</v>
       </c>
       <c r="B573" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C573" t="s">
         <v>7</v>
@@ -15023,13 +15024,13 @@
         <v>1</v>
       </c>
       <c r="E573" t="s">
+        <v>331</v>
+      </c>
+      <c r="F573" t="s">
         <v>332</v>
       </c>
-      <c r="F573" t="s">
-        <v>333</v>
-      </c>
       <c r="G573" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
@@ -15037,7 +15038,7 @@
         <v>40</v>
       </c>
       <c r="B574" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C574" t="s">
         <v>8</v>
@@ -15046,13 +15047,13 @@
         <v>1</v>
       </c>
       <c r="E574" t="s">
+        <v>331</v>
+      </c>
+      <c r="F574" t="s">
         <v>332</v>
       </c>
-      <c r="F574" t="s">
+      <c r="G574" t="s">
         <v>333</v>
-      </c>
-      <c r="G574" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
@@ -15060,7 +15061,7 @@
         <v>40</v>
       </c>
       <c r="B575" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C575" t="s">
         <v>6</v>
@@ -15069,7 +15070,7 @@
         <v>2</v>
       </c>
       <c r="E575" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
@@ -15077,7 +15078,7 @@
         <v>40</v>
       </c>
       <c r="B576" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C576" t="s">
         <v>7</v>
@@ -15086,13 +15087,13 @@
         <v>2</v>
       </c>
       <c r="E576" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F576" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G576" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
@@ -15100,7 +15101,7 @@
         <v>40</v>
       </c>
       <c r="B577" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C577" t="s">
         <v>8</v>
@@ -15109,13 +15110,13 @@
         <v>2</v>
       </c>
       <c r="E577" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F577" t="s">
+        <v>334</v>
+      </c>
+      <c r="G577" t="s">
         <v>335</v>
-      </c>
-      <c r="G577" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
@@ -15123,7 +15124,7 @@
         <v>40</v>
       </c>
       <c r="B578" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C578" t="s">
         <v>6</v>
@@ -15132,7 +15133,7 @@
         <v>3</v>
       </c>
       <c r="E578" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
@@ -15140,7 +15141,7 @@
         <v>40</v>
       </c>
       <c r="B579" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C579" t="s">
         <v>7</v>
@@ -15149,13 +15150,13 @@
         <v>3</v>
       </c>
       <c r="E579" t="s">
+        <v>336</v>
+      </c>
+      <c r="F579" t="s">
         <v>337</v>
       </c>
-      <c r="F579" t="s">
-        <v>338</v>
-      </c>
       <c r="G579" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
@@ -15163,7 +15164,7 @@
         <v>40</v>
       </c>
       <c r="B580" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C580" t="s">
         <v>8</v>
@@ -15172,13 +15173,13 @@
         <v>3</v>
       </c>
       <c r="E580" t="s">
+        <v>336</v>
+      </c>
+      <c r="F580" t="s">
         <v>337</v>
       </c>
-      <c r="F580" t="s">
+      <c r="G580" t="s">
         <v>338</v>
-      </c>
-      <c r="G580" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
@@ -15186,7 +15187,7 @@
         <v>40</v>
       </c>
       <c r="B581" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C581" t="s">
         <v>6</v>
@@ -15195,7 +15196,7 @@
         <v>4</v>
       </c>
       <c r="E581" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
@@ -15203,7 +15204,7 @@
         <v>40</v>
       </c>
       <c r="B582" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C582" t="s">
         <v>7</v>
@@ -15212,13 +15213,13 @@
         <v>4</v>
       </c>
       <c r="E582" t="s">
+        <v>339</v>
+      </c>
+      <c r="F582" t="s">
         <v>340</v>
       </c>
-      <c r="F582" t="s">
-        <v>341</v>
-      </c>
       <c r="G582" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
@@ -15226,7 +15227,7 @@
         <v>40</v>
       </c>
       <c r="B583" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C583" t="s">
         <v>8</v>
@@ -15235,13 +15236,13 @@
         <v>4</v>
       </c>
       <c r="E583" t="s">
+        <v>339</v>
+      </c>
+      <c r="F583" t="s">
         <v>340</v>
       </c>
-      <c r="F583" t="s">
+      <c r="G583" t="s">
         <v>341</v>
-      </c>
-      <c r="G583" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
@@ -15249,7 +15250,7 @@
         <v>40</v>
       </c>
       <c r="B584" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C584" t="s">
         <v>6</v>
@@ -15258,7 +15259,7 @@
         <v>5</v>
       </c>
       <c r="E584" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
@@ -15266,7 +15267,7 @@
         <v>40</v>
       </c>
       <c r="B585" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C585" t="s">
         <v>7</v>
@@ -15275,13 +15276,13 @@
         <v>5</v>
       </c>
       <c r="E585" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F585" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G585" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
@@ -15289,7 +15290,7 @@
         <v>40</v>
       </c>
       <c r="B586" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C586" t="s">
         <v>8</v>
@@ -15298,13 +15299,13 @@
         <v>5</v>
       </c>
       <c r="E586" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F586" t="s">
+        <v>342</v>
+      </c>
+      <c r="G586" t="s">
         <v>343</v>
-      </c>
-      <c r="G586" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
@@ -15312,7 +15313,7 @@
         <v>40</v>
       </c>
       <c r="B587" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C587" t="s">
         <v>6</v>
@@ -15321,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="E587" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
@@ -15329,7 +15330,7 @@
         <v>40</v>
       </c>
       <c r="B588" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C588" t="s">
         <v>7</v>
@@ -15338,13 +15339,13 @@
         <v>6</v>
       </c>
       <c r="E588" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F588" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G588" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
@@ -15352,7 +15353,7 @@
         <v>40</v>
       </c>
       <c r="B589" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C589" t="s">
         <v>8</v>
@@ -15361,13 +15362,13 @@
         <v>6</v>
       </c>
       <c r="E589" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F589" t="s">
+        <v>344</v>
+      </c>
+      <c r="G589" t="s">
         <v>345</v>
-      </c>
-      <c r="G589" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
@@ -15375,7 +15376,7 @@
         <v>40</v>
       </c>
       <c r="B590" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C590" t="s">
         <v>6</v>
@@ -15384,7 +15385,7 @@
         <v>7</v>
       </c>
       <c r="E590" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
@@ -15392,7 +15393,7 @@
         <v>40</v>
       </c>
       <c r="B591" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C591" t="s">
         <v>7</v>
@@ -15401,13 +15402,13 @@
         <v>7</v>
       </c>
       <c r="E591" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F591" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G591" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
@@ -15415,7 +15416,7 @@
         <v>40</v>
       </c>
       <c r="B592" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C592" t="s">
         <v>8</v>
@@ -15424,13 +15425,13 @@
         <v>7</v>
       </c>
       <c r="E592" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F592" t="s">
+        <v>346</v>
+      </c>
+      <c r="G592" t="s">
         <v>347</v>
-      </c>
-      <c r="G592" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
@@ -15438,7 +15439,7 @@
         <v>40</v>
       </c>
       <c r="B593" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C593" t="s">
         <v>6</v>
@@ -15447,7 +15448,7 @@
         <v>8</v>
       </c>
       <c r="E593" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
@@ -15455,7 +15456,7 @@
         <v>40</v>
       </c>
       <c r="B594" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C594" t="s">
         <v>7</v>
@@ -15464,13 +15465,13 @@
         <v>8</v>
       </c>
       <c r="E594" t="s">
+        <v>348</v>
+      </c>
+      <c r="F594" t="s">
         <v>349</v>
       </c>
-      <c r="F594" t="s">
-        <v>350</v>
-      </c>
       <c r="G594" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
@@ -15478,7 +15479,7 @@
         <v>40</v>
       </c>
       <c r="B595" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C595" t="s">
         <v>8</v>
@@ -15487,13 +15488,13 @@
         <v>8</v>
       </c>
       <c r="E595" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F595" t="s">
+        <v>349</v>
+      </c>
+      <c r="G595" t="s">
         <v>350</v>
-      </c>
-      <c r="G595" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
@@ -15501,7 +15502,7 @@
         <v>40</v>
       </c>
       <c r="B596" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C596" t="s">
         <v>6</v>
@@ -15510,7 +15511,7 @@
         <v>9</v>
       </c>
       <c r="E596" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
@@ -15518,7 +15519,7 @@
         <v>40</v>
       </c>
       <c r="B597" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C597" t="s">
         <v>7</v>
@@ -15527,13 +15528,13 @@
         <v>9</v>
       </c>
       <c r="E597" t="s">
+        <v>351</v>
+      </c>
+      <c r="F597" t="s">
         <v>352</v>
       </c>
-      <c r="F597" t="s">
-        <v>353</v>
-      </c>
       <c r="G597" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
@@ -15541,7 +15542,7 @@
         <v>40</v>
       </c>
       <c r="B598" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C598" t="s">
         <v>8</v>
@@ -15550,13 +15551,13 @@
         <v>9</v>
       </c>
       <c r="E598" t="s">
+        <v>351</v>
+      </c>
+      <c r="F598" t="s">
         <v>352</v>
       </c>
-      <c r="F598" t="s">
+      <c r="G598" t="s">
         <v>353</v>
-      </c>
-      <c r="G598" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
@@ -15564,7 +15565,7 @@
         <v>40</v>
       </c>
       <c r="B599" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C599" t="s">
         <v>6</v>
@@ -15573,7 +15574,7 @@
         <v>10</v>
       </c>
       <c r="E599" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
@@ -15581,7 +15582,7 @@
         <v>40</v>
       </c>
       <c r="B600" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C600" t="s">
         <v>7</v>
@@ -15590,13 +15591,13 @@
         <v>10</v>
       </c>
       <c r="E600" t="s">
+        <v>354</v>
+      </c>
+      <c r="F600" t="s">
         <v>355</v>
       </c>
-      <c r="F600" t="s">
-        <v>356</v>
-      </c>
       <c r="G600" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
@@ -15604,7 +15605,7 @@
         <v>40</v>
       </c>
       <c r="B601" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C601" t="s">
         <v>8</v>
@@ -15613,13 +15614,13 @@
         <v>10</v>
       </c>
       <c r="E601" t="s">
+        <v>354</v>
+      </c>
+      <c r="F601" t="s">
         <v>355</v>
       </c>
-      <c r="F601" t="s">
+      <c r="G601" t="s">
         <v>356</v>
-      </c>
-      <c r="G601" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -15905,7 +15906,7 @@
         <v>39</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>34</v>
+        <v>835</v>
       </c>
       <c r="C20" s="4">
         <v>30</v>
@@ -15919,7 +15920,7 @@
         <v>40</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4">
         <v>30</v>
@@ -15931,5 +15932,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>